--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5547-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5547-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BC80D0A-B42F-4510-A7B7-2B5028D5E919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B14FF3E-5E89-4BC4-9C36-FBCF7D0AD99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CD1B83AD-F8E5-4889-B4D6-A4AF0A75025E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{EC1D2E78-6BD4-430A-A398-C5F2DA7DF977}"/>
   </bookViews>
   <sheets>
     <sheet name="5547-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1466,20 +1466,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0214D7D8-66ED-4110-AFC3-146954393E3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0C74D8-FBFC-438F-9E45-86A1186150AE}">
   <dimension ref="A1:X13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1513,7 +1512,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1549,7 +1548,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1601,7 +1600,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1669,7 +1668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="13" t="s">
@@ -1769,7 +1768,7 @@
       <c r="W6" s="44"/>
       <c r="X6" s="40"/>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="45">
         <v>2023</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2022</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="45">
         <v>2021</v>
       </c>
@@ -1985,7 +1984,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2020</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37"/>
       <c r="B11" s="38"/>
       <c r="C11" s="13" t="s">
@@ -2085,7 +2084,7 @@
       <c r="W11" s="44"/>
       <c r="X11" s="40"/>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="45">
         <v>2019</v>
       </c>
@@ -2157,7 +2156,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>36</v>
       </c>
